--- a/Tablas/Tablas_Stock_2026_05.xlsx
+++ b/Tablas/Tablas_Stock_2026_05.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Arbol obstruye semaforo/luminaria/cartel: 47 casos con cierre 22%-&gt;49% (Abr-2026 a May-2026). Recuperacion marcada del cierre.</t>
+          <t>Arbol obstruye cierre critico: 47 casos, cierre 22%-&gt;49% (Abr-2026 a May-2026). Recuperacion del cierre.</t>
         </is>
       </c>
     </row>

--- a/Tablas/Tablas_Stock_2026_05.xlsx
+++ b/Tablas/Tablas_Stock_2026_05.xlsx
@@ -1196,17 +1196,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Cierre bajo - Vehículo mal estacionado</t>
+          <t>Cierre bajo - Vehiculo mal estacionado</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0% (22 casos)</t>
+          <t>22 casos, 0% cierre</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Tipo 'Vehículo mal estacionado': 22 casos en May-2026 con 0% de cierre (tablero). Cierre muy por debajo del resto del area.</t>
+          <t>Tipo 'Vehiculo mal estacionado': 22 casos en May-2026 que se registran en estado 'Sin asignar' (no se cierran), igual que en abril. Tipo implementado desde marzo 2026. No es demora operativa: revisar con el area si se estan siguiendo los protocolos de implementacion del proceso para tratar este tipo de reclamos.</t>
         </is>
       </c>
     </row>

--- a/Tablas/Tablas_Stock_2026_05.xlsx
+++ b/Tablas/Tablas_Stock_2026_05.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cierre global 74% (+0.0pp vs abril). CALLES Y VEREDAS en 15%, ARBOLADO 50%. ALUMBRADO 85% y RESIDUOS 81% lideran. Cancelado sobre cerrados alto en ARBOLADO 32%, TRANSITO 24%, CALLES 24%.</t>
+          <t>Cierre global 74% (+0.0pp vs abril). CALLES Y VEREDAS en 15%, ARBOLADO 50%. ALUMBRADO 85% y RESIDUOS 81% lideran. Cancelado sobre cerrados alto en ARBOLADO 32%, CALLES 25%, TRANSITO 24%.</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SLA global 45% (+4.0pp vs abril). CTRL ACT COMERCIALES 23% y CTRL ESPACIO PUBLICO 26% bajos. ALUMBRADO lidera con 71%, TRANSITO 58%. Promedio 3 dias.</t>
+          <t>SLA global 44% (+3.0pp vs abril). TRANSITO 31% y CTRL ACT COMERCIALES 30% bajos. ALUMBRADO lidera con 71%, RESIDUOS 40%, ARBOLADO 45%. Promedio 3 dias.</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cierre critico 15% sobre 290 incidentes; 'Bache en calle de asfalto' lidera con 101 casos (19% cierre). Sat 50% (muestra insuficiente).</t>
+          <t>Cierre critico 15% sobre 292 incidentes; 'Bache en calle de asfalto' lidera con 101 casos (19% cierre). Sat 50% (muestra insuficiente).</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cierre moderado 60% sobre 88 incidentes; 'Otros ruidos molestos' lidera con 28 casos (54% cierre). SLA 23% bajo.</t>
+          <t>Cierre moderado 60% sobre 88 incidentes; 'Otros ruidos molestos' lidera con 28 casos (54% cierre). SLA 30%, sat 67%.</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cierre 72% sobre 350 incidentes; 'Roedores en espacio público' lidera con 214 casos (95% cierre). SLA 26% bajo.</t>
+          <t>Cierre 72% sobre 348 incidentes; 'Roedores en espacio público' lidera con 214 casos (95% cierre). SLA 50%, sat 53%.</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Abr-2026</t>
+          <t>Feb-2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Dias promedio alto</t>
+          <t>SLA critico</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5 dias</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiempo promedio de resolucion baja a 5 dias en May-2026 (tablero). Vuelve a parametro habitual.</t>
+          <t>SLA sube a 30% en May-2026 (tablero), sale de zona critica.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Abr-2026</t>
+          <t>Feb-2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cierre bajo - Cable cortado</t>
+          <t>SLA por area</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4%-&gt;72%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Cierre del area sube de 4% a 72% (Abr-2026 a May-2026). Recuperacion significativa.</t>
+          <t>SLA sube a 50% en May-2026 (tablero), sale de zona critica.</t>
         </is>
       </c>
     </row>
@@ -839,86 +839,86 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>Control de Actividades Comerciales</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Dias promedio alto</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5 dias</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Tiempo promedio de resolucion baja a 5 dias en May-2026 (tablero). Vuelve a parametro habitual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RESUELTA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Abr-2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Control del Espacio Publico</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Cierre bajo - Cable cortado</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4%-&gt;72%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Cierre del area sube de 4% a 72% (Abr-2026 a May-2026). Recuperacion significativa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RESUELTA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Abr-2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Residuos y Limpieza</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Cierre bajo - Falta de recolección de residuos reciclables (Pr</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>27%-&gt;81%</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Cierre del area sube de 27% a 81% (Abr-2026 a May-2026). Recuperacion significativa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>PERSISTE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Feb-2026</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Arbolado y Plazas</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>% Cancelado &gt;10%</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>32% (sobre cerrados)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Cancelado 32% de los cerrados en May-2026 (donut Cierres por Estado). Proporcion elevada que persiste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>PERSISTE</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Mar-2026</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Calles y Veredas</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Cierre colapsado</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>7%-&gt;15%</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Cierre del area 7%-&gt;15% (Abr-2026 a May-2026). Sigue en zona critica. Cancelado 24% sobre cerrados.</t>
         </is>
       </c>
     </row>
@@ -935,22 +935,22 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Control de Actividades Comerciales</t>
+          <t>Arbolado y Plazas</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>SLA critico</t>
+          <t>% Cancelado &gt;10%</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>32% (sobre cerrados)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>SLA 23% en May-2026 (tablero), persiste en niveles bajos.</t>
+          <t>Cancelado 32% de los cerrados en May-2026 (donut Cierres por Estado). Proporcion elevada que persiste.</t>
         </is>
       </c>
     </row>
@@ -962,27 +962,27 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Feb-2026</t>
+          <t>Mar-2026</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Control del Espacio Publico</t>
+          <t>Calles y Veredas</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>SLA por area</t>
+          <t>Cierre colapsado</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>7%-&gt;15%</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>SLA 26% en May-2026 (tablero), persiste en niveles bajos.</t>
+          <t>Cierre del area 7%-&gt;15% (Abr-2026 a May-2026). Sigue en zona critica. Cancelado 25% sobre cerrados.</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>24% (sobre cerrados)</t>
+          <t>25% (sobre cerrados)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Cancelado 24% de los cerrados en May-2026 (donut Cierres por Estado). Proporcion elevada que persiste.</t>
+          <t>Cancelado 25% de los cerrados en May-2026 (donut Cierres por Estado). Proporcion elevada que persiste.</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Tasa de respuesta encuesta 2.1% (6 respuestas sobre 290 incidentes) en May-2026. Datos de satisfaccion no representativos.</t>
+          <t>Tasa de respuesta encuesta 2.1% (6 respuestas sobre 292 incidentes) en May-2026. Datos de satisfaccion no representativos.</t>
         </is>
       </c>
     </row>
